--- a/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
+++ b/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
@@ -587,22 +587,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20446596.21263622</v>
+        <v>20384168.92853245</v>
       </c>
       <c r="E5" t="n">
-        <v>20925674.64079577</v>
+        <v>20855788.36444836</v>
       </c>
       <c r="F5" t="n">
-        <v>835729.7726826507</v>
+        <v>837388.4246924805</v>
       </c>
       <c r="G5" t="n">
-        <v>17313363.84117422</v>
+        <v>17443090.92244567</v>
       </c>
       <c r="H5" t="n">
-        <v>703409.5804538094</v>
+        <v>833136.6617252566</v>
       </c>
       <c r="I5" t="n">
-        <v>4.234867654736702</v>
+        <v>5.015887754101024</v>
       </c>
     </row>
   </sheetData>
@@ -861,43 +861,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6958725.731837421</v>
+        <v>6639128.810765962</v>
       </c>
       <c r="D5" t="n">
-        <v>5636567.842788313</v>
+        <v>5377694.336720429</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4993146019981885</v>
+        <v>0.5241959583397854</v>
       </c>
       <c r="F5" t="n">
-        <v>1.124842903355472</v>
+        <v>1.155258472708051</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6255283013572834</v>
+        <v>0.6310625143682657</v>
       </c>
       <c r="H5" t="n">
-        <v>53.53619007665776</v>
+        <v>42.91327066136493</v>
       </c>
       <c r="I5" t="n">
-        <v>68.07383178775387</v>
+        <v>71.24771614752423</v>
       </c>
       <c r="J5" t="n">
-        <v>13137263.41385045</v>
+        <v>13270610.11386495</v>
       </c>
       <c r="K5" t="n">
-        <v>465067.1895622708</v>
+        <v>461000.4998625214</v>
       </c>
       <c r="L5" t="n">
-        <v>3711033.237761501</v>
+        <v>3711480.308718203</v>
       </c>
       <c r="M5" t="n">
-        <v>17313363.84117422</v>
+        <v>17443090.92244567</v>
       </c>
       <c r="N5" t="n">
-        <v>835729.7726826507</v>
+        <v>837388.4246924804</v>
       </c>
       <c r="O5" t="n">
-        <v>9260</v>
+        <v>9266</v>
       </c>
     </row>
   </sheetData>
@@ -970,16 +970,16 @@
         <v>40587.35712485121</v>
       </c>
       <c r="E2" t="n">
-        <v>67411.18084629629</v>
+        <v>67383.60064958848</v>
       </c>
       <c r="F2" t="n">
-        <v>69188.25712098765</v>
+        <v>69391.51544683333</v>
       </c>
       <c r="G2" t="n">
-        <v>3013.450281893004</v>
+        <v>2869.685866666668</v>
       </c>
       <c r="H2" t="n">
-        <v>57991.41227085391</v>
+        <v>58267.76122776201</v>
       </c>
     </row>
     <row r="3">
@@ -996,16 +996,16 @@
         <v>15478.71530669584</v>
       </c>
       <c r="E3" t="n">
-        <v>34290.87456481481</v>
+        <v>33899.99171666666</v>
       </c>
       <c r="F3" t="n">
-        <v>34899.27216481481</v>
+        <v>34508.38931666667</v>
       </c>
       <c r="G3" t="n">
         <v>1081.070016666666</v>
       </c>
       <c r="H3" t="n">
-        <v>19737.4122983475</v>
+        <v>20191.59679172417</v>
       </c>
     </row>
     <row r="4">
@@ -1022,16 +1022,16 @@
         <v>42728.75851619014</v>
       </c>
       <c r="E4" t="n">
-        <v>68276.87073971193</v>
+        <v>68149.93810955968</v>
       </c>
       <c r="F4" t="n">
-        <v>68276.87073971193</v>
+        <v>68149.93810955968</v>
       </c>
       <c r="G4" t="n">
-        <v>3210.142636833331</v>
+        <v>3215.938223666667</v>
       </c>
       <c r="H4" t="n">
-        <v>59100.79988739513</v>
+        <v>59872.78863840146</v>
       </c>
     </row>
     <row r="5">
@@ -1048,16 +1048,16 @@
         <v>69691.38024403834</v>
       </c>
       <c r="E5" t="n">
-        <v>93776.07118950615</v>
+        <v>93776.07118950617</v>
       </c>
       <c r="F5" t="n">
-        <v>94550.43078333333</v>
+        <v>94583.89830925924</v>
       </c>
       <c r="G5" t="n">
-        <v>2467.360283333334</v>
+        <v>2465.557035333338</v>
       </c>
       <c r="H5" t="n">
-        <v>85107.66413952866</v>
+        <v>85325.66943503436</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
+++ b/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>69691.38024403834</v>
+        <v>69691.38024403836</v>
       </c>
       <c r="E5" t="n">
         <v>93776.07118950617</v>

--- a/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
+++ b/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,9 +50,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,18 +482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>实际负荷、实际光伏</t>
+          <t>历史联合情景</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20218838.18025311</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>21030208.70695398</v>
+      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>200482.5499791485</v>
       </c>
       <c r="G2" t="n">
-        <v>12245046.91527763</v>
+        <v>14317166.48169138</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -515,24 +514,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>实际负荷、实际光伏</t>
+          <t>历史联合情景</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20273062.2199353</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>21084870.83058419</v>
+      </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>198238.4629259463</v>
       </c>
       <c r="G3" t="n">
-        <v>12830486.38665614</v>
+        <v>15127992.55440778</v>
       </c>
       <c r="H3" t="n">
-        <v>585439.4713785071</v>
+        <v>810826.0727163982</v>
       </c>
       <c r="I3" t="n">
-        <v>4.781030856223826</v>
+        <v>5.663313853011857</v>
       </c>
     </row>
     <row r="4">
@@ -548,20 +546,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>附件3滚动光伏预报</t>
+          <t>附件3预报+联合情景</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20385219.03615807</v>
+        <v>21024772.78771503</v>
       </c>
       <c r="E4" t="n">
-        <v>20860687.28821348</v>
+        <v>21236928.82470027</v>
       </c>
       <c r="F4" t="n">
-        <v>835168.1400457479</v>
+        <v>40496.48242637002</v>
       </c>
       <c r="G4" t="n">
-        <v>16609954.26072041</v>
+        <v>13736332.08170742</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -583,26 +581,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>附件3滚动光伏预报</t>
+          <t>附件3预报+联合情景</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20384168.92853245</v>
+        <v>21059204.84515597</v>
       </c>
       <c r="E5" t="n">
-        <v>20855788.36444836</v>
+        <v>21277381.12831469</v>
       </c>
       <c r="F5" t="n">
-        <v>837388.4246924805</v>
+        <v>40104.45617451196</v>
       </c>
       <c r="G5" t="n">
-        <v>17443090.92244567</v>
+        <v>14491465.26514751</v>
       </c>
       <c r="H5" t="n">
-        <v>833136.6617252566</v>
+        <v>755133.1834400948</v>
       </c>
       <c r="I5" t="n">
-        <v>5.015887754101024</v>
+        <v>5.497342223152137</v>
       </c>
     </row>
   </sheetData>
@@ -708,43 +706,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6786739.973548971</v>
+        <v>6581075.983121438</v>
       </c>
       <c r="D2" t="n">
-        <v>5497259.378574667</v>
+        <v>5327940.463471066</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5220455724399419</v>
+        <v>0.5366062397556842</v>
       </c>
       <c r="F2" t="n">
-        <v>1.140349681321089</v>
+        <v>1.079318053532384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6183041088811475</v>
+        <v>0.5427118137767001</v>
       </c>
       <c r="H2" t="n">
-        <v>49.32362632493295</v>
+        <v>49.32357079266279</v>
       </c>
       <c r="I2" t="n">
-        <v>69.16955635814593</v>
+        <v>63.411879985717</v>
       </c>
       <c r="J2" t="n">
-        <v>12245046.91527763</v>
+        <v>13182469.5281936</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1134696.95349778</v>
       </c>
       <c r="M2" t="n">
-        <v>12245046.91527763</v>
+        <v>14317166.48169138</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>200482.5499791485</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="3">
@@ -759,43 +757,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7072260.242970164</v>
+        <v>6401631.849485602</v>
       </c>
       <c r="D3" t="n">
-        <v>5728530.796805833</v>
+        <v>5182407.468929213</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4953152771652075</v>
+        <v>0.5236832945354639</v>
       </c>
       <c r="F3" t="n">
-        <v>1.133156461902561</v>
+        <v>1.10767819356767</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6378411847373539</v>
+        <v>0.5839948990322061</v>
       </c>
       <c r="H3" t="n">
-        <v>53.97612062466791</v>
+        <v>46.65778583687474</v>
       </c>
       <c r="I3" t="n">
-        <v>69.47557514233549</v>
+        <v>67.31953186392823</v>
       </c>
       <c r="J3" t="n">
-        <v>12830486.38665613</v>
+        <v>13904893.47043311</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1223099.083974668</v>
       </c>
       <c r="M3" t="n">
-        <v>12830486.38665613</v>
+        <v>15127992.55440778</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>198238.4629259463</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="4">
@@ -810,43 +808,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6654617.407021193</v>
+        <v>6553176.061106154</v>
       </c>
       <c r="D4" t="n">
-        <v>5390240.099687167</v>
+        <v>5303620.752581966</v>
       </c>
       <c r="E4" t="n">
-        <v>0.525360603951988</v>
+        <v>0.5361283334957533</v>
       </c>
       <c r="F4" t="n">
-        <v>1.132690439597055</v>
+        <v>1.080937978533518</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6073298356450669</v>
+        <v>0.5448096450377652</v>
       </c>
       <c r="H4" t="n">
-        <v>47.59261734901294</v>
+        <v>49.37518529502662</v>
       </c>
       <c r="I4" t="n">
-        <v>68.32692965577573</v>
+        <v>64.05533419864588</v>
       </c>
       <c r="J4" t="n">
-        <v>12570533.91378646</v>
+        <v>13180233.87674109</v>
       </c>
       <c r="K4" t="n">
-        <v>434755.752374651</v>
+        <v>340540.9345122612</v>
       </c>
       <c r="L4" t="n">
-        <v>3604664.594559303</v>
+        <v>215557.2704540688</v>
       </c>
       <c r="M4" t="n">
-        <v>16609954.26072041</v>
+        <v>13736332.08170742</v>
       </c>
       <c r="N4" t="n">
-        <v>835168.1400457479</v>
+        <v>40496.48242637003</v>
       </c>
       <c r="O4" t="n">
-        <v>9251</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5">
@@ -861,43 +859,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6639128.810765962</v>
+        <v>6387094.631567797</v>
       </c>
       <c r="D5" t="n">
-        <v>5377694.336720429</v>
+        <v>5168812.34584623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5241959583397854</v>
+        <v>0.5228169032391917</v>
       </c>
       <c r="F5" t="n">
-        <v>1.155258472708051</v>
+        <v>1.108270108772137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6310625143682657</v>
+        <v>0.5854532055329457</v>
       </c>
       <c r="H5" t="n">
-        <v>42.91327066136493</v>
+        <v>46.82611417680073</v>
       </c>
       <c r="I5" t="n">
-        <v>71.24771614752423</v>
+        <v>67.8299662211661</v>
       </c>
       <c r="J5" t="n">
-        <v>13270610.11386495</v>
+        <v>13893960.08359633</v>
       </c>
       <c r="K5" t="n">
-        <v>461000.4998625214</v>
+        <v>369082.8541044205</v>
       </c>
       <c r="L5" t="n">
-        <v>3711480.308718203</v>
+        <v>228422.3274467576</v>
       </c>
       <c r="M5" t="n">
-        <v>17443090.92244567</v>
+        <v>14491465.26514751</v>
       </c>
       <c r="N5" t="n">
-        <v>837388.4246924804</v>
+        <v>40104.45617451196</v>
       </c>
       <c r="O5" t="n">
-        <v>9266</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -957,107 +955,107 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="B2" t="n">
-        <v>66316.8114583498</v>
+        <v>72942.0362627397</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>402.0538900833399</v>
       </c>
       <c r="D2" t="n">
-        <v>40587.35712485121</v>
+        <v>47715.79114460137</v>
       </c>
       <c r="E2" t="n">
-        <v>67383.60064958848</v>
+        <v>72641.2507989537</v>
       </c>
       <c r="F2" t="n">
-        <v>69391.51544683333</v>
+        <v>72648.80189478703</v>
       </c>
       <c r="G2" t="n">
-        <v>2869.685866666668</v>
+        <v>394.5027942500062</v>
       </c>
       <c r="H2" t="n">
-        <v>58267.76122776201</v>
+        <v>47554.21084528161</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="B3" t="n">
-        <v>33229.13910884774</v>
+        <v>36037.35884483084</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="D3" t="n">
-        <v>15478.71530669584</v>
+        <v>19233.91543714997</v>
       </c>
       <c r="E3" t="n">
-        <v>33899.99171666666</v>
+        <v>36037.35884483084</v>
       </c>
       <c r="F3" t="n">
-        <v>34508.38931666667</v>
+        <v>36037.35884483084</v>
       </c>
       <c r="G3" t="n">
-        <v>1081.070016666666</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="H3" t="n">
-        <v>20191.59679172417</v>
+        <v>19233.91543714997</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>66265.42130905349</v>
+        <v>68276.81518487277</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>6.375000000000114</v>
       </c>
       <c r="D4" t="n">
-        <v>42728.75851619014</v>
+        <v>46306.16567797329</v>
       </c>
       <c r="E4" t="n">
-        <v>68149.93810955968</v>
+        <v>68276.81518487277</v>
       </c>
       <c r="F4" t="n">
-        <v>68149.93810955968</v>
+        <v>68276.81518487277</v>
       </c>
       <c r="G4" t="n">
-        <v>3215.938223666667</v>
+        <v>6.375000000000114</v>
       </c>
       <c r="H4" t="n">
-        <v>59872.78863840146</v>
+        <v>46306.16567797329</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46012</v>
       </c>
       <c r="B5" t="n">
-        <v>93770.21493971194</v>
+        <v>92691.37131000659</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>391.4820369999948</v>
       </c>
       <c r="D5" t="n">
-        <v>69691.38024403836</v>
+        <v>74641.41316872055</v>
       </c>
       <c r="E5" t="n">
-        <v>93776.07118950617</v>
+        <v>92381.8599591614</v>
       </c>
       <c r="F5" t="n">
-        <v>94583.89830925924</v>
+        <v>92822.6187254613</v>
       </c>
       <c r="G5" t="n">
-        <v>2465.557035333338</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="H5" t="n">
-        <v>85325.66943503436</v>
+        <v>72413.89904571924</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
+++ b/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,10 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,13 +486,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21030208.70695398</v>
-      </c>
+        <v>20626391.62229223</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>200482.5499791485</v>
+        <v>225899.8993864736</v>
       </c>
       <c r="G2" t="n">
-        <v>14317166.48169138</v>
+        <v>14000626.94601158</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -518,19 +519,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21084870.83058419</v>
-      </c>
+        <v>20621184.5546696</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>198238.4629259463</v>
+        <v>226734.080774127</v>
       </c>
       <c r="G3" t="n">
-        <v>15127992.55440778</v>
+        <v>14764806.63295469</v>
       </c>
       <c r="H3" t="n">
-        <v>810826.0727163982</v>
+        <v>764179.6869431026</v>
       </c>
       <c r="I3" t="n">
-        <v>5.663313853011857</v>
+        <v>5.458181907780905</v>
       </c>
     </row>
     <row r="4">
@@ -550,16 +552,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21024772.78771503</v>
+        <v>21019054.85541281</v>
       </c>
       <c r="E4" t="n">
-        <v>21236928.82470027</v>
+        <v>21346032.78454667</v>
       </c>
       <c r="F4" t="n">
-        <v>40496.48242637002</v>
+        <v>39058.92704752037</v>
       </c>
       <c r="G4" t="n">
-        <v>13736332.08170742</v>
+        <v>13716608.07054248</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -585,22 +587,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21059204.84515597</v>
+        <v>21052571.97073786</v>
       </c>
       <c r="E5" t="n">
-        <v>21277381.12831469</v>
+        <v>21397739.14961106</v>
       </c>
       <c r="F5" t="n">
-        <v>40104.45617451196</v>
+        <v>37876.25901956838</v>
       </c>
       <c r="G5" t="n">
-        <v>14491465.26514751</v>
+        <v>14485826.67858481</v>
       </c>
       <c r="H5" t="n">
-        <v>755133.1834400948</v>
+        <v>769218.6080423333</v>
       </c>
       <c r="I5" t="n">
-        <v>5.497342223152137</v>
+        <v>5.607936044292846</v>
       </c>
     </row>
   </sheetData>
@@ -706,43 +708,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6581075.983121438</v>
+        <v>6301525.602080986</v>
       </c>
       <c r="D2" t="n">
-        <v>5327940.463471066</v>
+        <v>5106592.628911074</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5366062397556842</v>
+        <v>0.5433813937802582</v>
       </c>
       <c r="F2" t="n">
-        <v>1.079318053532384</v>
+        <v>1.140702436193685</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5427118137767001</v>
+        <v>0.5973210424134264</v>
       </c>
       <c r="H2" t="n">
-        <v>49.32357079266279</v>
+        <v>46.34220442183645</v>
       </c>
       <c r="I2" t="n">
-        <v>63.411879985717</v>
+        <v>69.62000355901387</v>
       </c>
       <c r="J2" t="n">
-        <v>13182469.5281936</v>
+        <v>12783979.361277</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1134696.95349778</v>
+        <v>1216647.584734584</v>
       </c>
       <c r="M2" t="n">
-        <v>14317166.48169138</v>
+        <v>14000626.94601158</v>
       </c>
       <c r="N2" t="n">
-        <v>200482.5499791485</v>
+        <v>225899.8993864736</v>
       </c>
       <c r="O2" t="n">
-        <v>1677</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="3">
@@ -757,43 +759,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6401631.849485602</v>
+        <v>6281476.795265058</v>
       </c>
       <c r="D3" t="n">
-        <v>5182407.468929213</v>
+        <v>5090470.572832718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5236832945354639</v>
+        <v>0.5353236973822485</v>
       </c>
       <c r="F3" t="n">
-        <v>1.10767819356767</v>
+        <v>1.160541076868357</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5839948990322061</v>
+        <v>0.6252173794861086</v>
       </c>
       <c r="H3" t="n">
-        <v>46.65778583687474</v>
+        <v>45.2962124958396</v>
       </c>
       <c r="I3" t="n">
-        <v>67.31953186392823</v>
+        <v>71.68463014818008</v>
       </c>
       <c r="J3" t="n">
-        <v>13904893.47043311</v>
+        <v>13492763.07023848</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1223099.083974668</v>
+        <v>1272043.562716207</v>
       </c>
       <c r="M3" t="n">
-        <v>15127992.55440778</v>
+        <v>14764806.63295469</v>
       </c>
       <c r="N3" t="n">
-        <v>198238.4629259463</v>
+        <v>226734.080774127</v>
       </c>
       <c r="O3" t="n">
-        <v>1496</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="4">
@@ -808,43 +810,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6553176.061106154</v>
+        <v>6641743.526326237</v>
       </c>
       <c r="D4" t="n">
-        <v>5303620.752581966</v>
+        <v>5375360.399410234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5361283334957533</v>
+        <v>0.533928173726637</v>
       </c>
       <c r="F4" t="n">
-        <v>1.080937978533518</v>
+        <v>1.085253431482321</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5448096450377652</v>
+        <v>0.5513252577556838</v>
       </c>
       <c r="H4" t="n">
-        <v>49.37518529502662</v>
+        <v>48.57956646945435</v>
       </c>
       <c r="I4" t="n">
-        <v>64.05533419864588</v>
+        <v>64.74449886070693</v>
       </c>
       <c r="J4" t="n">
-        <v>13180233.87674109</v>
+        <v>13177906.76377876</v>
       </c>
       <c r="K4" t="n">
-        <v>340540.9345122612</v>
+        <v>332798.125078431</v>
       </c>
       <c r="L4" t="n">
-        <v>215557.2704540688</v>
+        <v>205903.1816852831</v>
       </c>
       <c r="M4" t="n">
-        <v>13736332.08170742</v>
+        <v>13716608.07054248</v>
       </c>
       <c r="N4" t="n">
-        <v>40496.48242637003</v>
+        <v>39058.92704752037</v>
       </c>
       <c r="O4" t="n">
-        <v>538</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5">
@@ -859,43 +861,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6387094.631567797</v>
+        <v>6478109.106533493</v>
       </c>
       <c r="D5" t="n">
-        <v>5168812.34584623</v>
+        <v>5242534.070568444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5228169032391917</v>
+        <v>0.5216260435430341</v>
       </c>
       <c r="F5" t="n">
-        <v>1.108270108772137</v>
+        <v>1.114168051978186</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5854532055329457</v>
+        <v>0.5925420084351517</v>
       </c>
       <c r="H5" t="n">
-        <v>46.82611417680073</v>
+        <v>48.95806785577923</v>
       </c>
       <c r="I5" t="n">
-        <v>67.8299662211661</v>
+        <v>68.06676237546107</v>
       </c>
       <c r="J5" t="n">
-        <v>13893960.08359633</v>
+        <v>13891179.02223154</v>
       </c>
       <c r="K5" t="n">
-        <v>369082.8541044205</v>
+        <v>380992.70972952</v>
       </c>
       <c r="L5" t="n">
-        <v>228422.3274467576</v>
+        <v>213654.9466237525</v>
       </c>
       <c r="M5" t="n">
-        <v>14491465.26514751</v>
+        <v>14485826.67858482</v>
       </c>
       <c r="N5" t="n">
-        <v>40104.45617451196</v>
+        <v>37876.25901956838</v>
       </c>
       <c r="O5" t="n">
-        <v>546</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -955,43 +957,43 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>45736</v>
       </c>
       <c r="B2" t="n">
-        <v>72942.0362627397</v>
+        <v>62089.91623638064</v>
       </c>
       <c r="C2" t="n">
+        <v>3649.041875140923</v>
+      </c>
+      <c r="D2" t="n">
+        <v>60473.08207684428</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72545.07421109361</v>
+      </c>
+      <c r="F2" t="n">
+        <v>72545.07421109361</v>
+      </c>
+      <c r="G2" t="n">
         <v>402.0538900833399</v>
       </c>
-      <c r="D2" t="n">
-        <v>47715.79114460137</v>
-      </c>
-      <c r="E2" t="n">
-        <v>72641.2507989537</v>
-      </c>
-      <c r="F2" t="n">
-        <v>72648.80189478703</v>
-      </c>
-      <c r="G2" t="n">
-        <v>394.5027942500062</v>
-      </c>
       <c r="H2" t="n">
-        <v>47554.21084528161</v>
+        <v>47545.25624721422</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>45829</v>
       </c>
       <c r="B3" t="n">
-        <v>36037.35884483084</v>
+        <v>34120.55166182398</v>
       </c>
       <c r="C3" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>172.6704773190164</v>
       </c>
       <c r="D3" t="n">
-        <v>19233.91543714997</v>
+        <v>17779.1949830534</v>
       </c>
       <c r="E3" t="n">
         <v>36037.35884483084</v>
@@ -1007,17 +1009,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>68276.81518487277</v>
+        <v>65407.62671049626</v>
       </c>
       <c r="C4" t="n">
-        <v>6.375000000000114</v>
+        <v>539.7345078629594</v>
       </c>
       <c r="D4" t="n">
-        <v>46306.16567797329</v>
+        <v>47256.76481201575</v>
       </c>
       <c r="E4" t="n">
         <v>68276.81518487277</v>
@@ -1033,29 +1035,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46012</v>
       </c>
       <c r="B5" t="n">
-        <v>92691.37131000659</v>
+        <v>96350.09431121967</v>
       </c>
       <c r="C5" t="n">
-        <v>391.4820369999948</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>74641.41316872055</v>
+        <v>73296.12167669171</v>
       </c>
       <c r="E5" t="n">
         <v>92381.8599591614</v>
       </c>
       <c r="F5" t="n">
-        <v>92822.6187254613</v>
+        <v>94277.82924709134</v>
       </c>
       <c r="G5" t="n">
         <v>2.273736754432321e-13</v>
       </c>
       <c r="H5" t="n">
-        <v>72413.89904571924</v>
+        <v>73698.54685448857</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
+++ b/问题四/output/问题2_3与问题4_2_4_3_对比.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全年费用对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略指标" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指定日期对比" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预报更新方案对比" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,16 +553,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21019054.85541281</v>
+        <v>21019065.316085</v>
       </c>
       <c r="E4" t="n">
-        <v>21346032.78454667</v>
+        <v>21346012.26097453</v>
       </c>
       <c r="F4" t="n">
-        <v>39058.92704752037</v>
+        <v>39056.96099439537</v>
       </c>
       <c r="G4" t="n">
-        <v>13716608.07054248</v>
+        <v>13716558.41341808</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -587,22 +588,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21052571.97073786</v>
+        <v>21052570.69847152</v>
       </c>
       <c r="E5" t="n">
-        <v>21397739.14961106</v>
+        <v>21397740.38640086</v>
       </c>
       <c r="F5" t="n">
         <v>37876.25901956838</v>
       </c>
       <c r="G5" t="n">
-        <v>14485826.67858481</v>
+        <v>14485814.58758956</v>
       </c>
       <c r="H5" t="n">
-        <v>769218.6080423333</v>
+        <v>769256.1741714776</v>
       </c>
       <c r="I5" t="n">
-        <v>5.607936044292846</v>
+        <v>5.608230220628528</v>
       </c>
     </row>
   </sheetData>
@@ -810,40 +811,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6641743.526326237</v>
+        <v>6641731.133020219</v>
       </c>
       <c r="D4" t="n">
-        <v>5375360.399410234</v>
+        <v>5375350.360832359</v>
       </c>
       <c r="E4" t="n">
-        <v>0.533928173726637</v>
+        <v>0.5339281966964934</v>
       </c>
       <c r="F4" t="n">
-        <v>1.085253431482321</v>
+        <v>1.085256162228804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5513252577556838</v>
+        <v>0.5513279655323108</v>
       </c>
       <c r="H4" t="n">
-        <v>48.57956646945435</v>
+        <v>48.57947270722076</v>
       </c>
       <c r="I4" t="n">
-        <v>64.74449886070693</v>
+        <v>64.74485921691654</v>
       </c>
       <c r="J4" t="n">
-        <v>13177906.76377876</v>
+        <v>13177911.98633694</v>
       </c>
       <c r="K4" t="n">
-        <v>332798.125078431</v>
+        <v>332756.9605824561</v>
       </c>
       <c r="L4" t="n">
-        <v>205903.1816852831</v>
+        <v>205889.4664986831</v>
       </c>
       <c r="M4" t="n">
-        <v>13716608.07054248</v>
+        <v>13716558.41341808</v>
       </c>
       <c r="N4" t="n">
-        <v>39058.92704752037</v>
+        <v>39056.96099439537</v>
       </c>
       <c r="O4" t="n">
         <v>520</v>
@@ -861,37 +862,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6478109.106533493</v>
+        <v>6478115.615953521</v>
       </c>
       <c r="D5" t="n">
-        <v>5242534.070568444</v>
+        <v>5242539.343198666</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5216260435430341</v>
+        <v>0.5216249110123582</v>
       </c>
       <c r="F5" t="n">
-        <v>1.114168051978186</v>
+        <v>1.11416775397561</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5925420084351517</v>
+        <v>0.5925428429632519</v>
       </c>
       <c r="H5" t="n">
-        <v>48.95806785577923</v>
+        <v>48.95801866112969</v>
       </c>
       <c r="I5" t="n">
-        <v>68.06676237546107</v>
+        <v>68.06669391801231</v>
       </c>
       <c r="J5" t="n">
-        <v>13891179.02223154</v>
+        <v>13891178.44375939</v>
       </c>
       <c r="K5" t="n">
-        <v>380992.70972952</v>
+        <v>380981.1972064177</v>
       </c>
       <c r="L5" t="n">
         <v>213654.9466237525</v>
       </c>
       <c r="M5" t="n">
-        <v>14485826.67858482</v>
+        <v>14485814.58758956</v>
       </c>
       <c r="N5" t="n">
         <v>37876.25901956838</v>
@@ -1063,4 +1064,240 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>情景</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>计划购电量_kWh</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>调整购电量_kWh</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>紧急购电量_kWh</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>计划购电费_元</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>调整费用_元</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>紧急购电费_元</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>总费用_元</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>更新接受次数</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>更新拒绝次数</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>保持计划不可行次数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>预计调整节省_元</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>仅0:00预报</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21052570.69847152</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21052570.69847152</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197397.0901984647</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13891178.44375939</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1251638.204462913</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15142816.6482223</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>更新至6:00</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>21052570.69847152</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21495762.03385943</v>
+      </c>
+      <c r="D3" t="n">
+        <v>72388.49955969074</v>
+      </c>
+      <c r="E3" t="n">
+        <v>13891178.44375939</v>
+      </c>
+      <c r="F3" t="n">
+        <v>424637.4622904298</v>
+      </c>
+      <c r="G3" t="n">
+        <v>462482.9570900864</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14778298.8631399</v>
+      </c>
+      <c r="I3" t="n">
+        <v>222</v>
+      </c>
+      <c r="J3" t="n">
+        <v>112</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>363653.2215192697</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>更新至12:00</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21052570.69847152</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21454371.14038518</v>
+      </c>
+      <c r="D4" t="n">
+        <v>57004.87271472684</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13891178.44375939</v>
+      </c>
+      <c r="F4" t="n">
+        <v>380656.6979932446</v>
+      </c>
+      <c r="G4" t="n">
+        <v>349750.1741053474</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14621585.31585798</v>
+      </c>
+      <c r="I4" t="n">
+        <v>434</v>
+      </c>
+      <c r="J4" t="n">
+        <v>234</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>501810.7603520461</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>更新至18:00</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21052570.69847152</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21397740.38640086</v>
+      </c>
+      <c r="D5" t="n">
+        <v>37876.25901956838</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13891178.44375939</v>
+      </c>
+      <c r="F5" t="n">
+        <v>380981.1972064177</v>
+      </c>
+      <c r="G5" t="n">
+        <v>213654.9466237525</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14485814.58758956</v>
+      </c>
+      <c r="I5" t="n">
+        <v>556</v>
+      </c>
+      <c r="J5" t="n">
+        <v>446</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>549939.1264143392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>